--- a/targets/TargetSheet.xlsx
+++ b/targets/TargetSheet.xlsx
@@ -986,7 +986,7 @@
     <row r="3" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10"/>
       <c r="B3" s="11" t="n">
-        <v>1400000</v>
+        <v>1500000</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
